--- a/templates/weekly_disclosure.xlsx
+++ b/templates/weekly_disclosure.xlsx
@@ -44,7 +44,7 @@
     <t>CVE编号</t>
   </si>
   <si>
-    <t>CNVD编号</t>
+    <t>漏洞编号</t>
   </si>
   <si>
     <t>影响产品</t>
